--- a/XLibur.Tests/Resource/Examples/PageSetup/SheetTab.xlsx
+++ b/XLibur.Tests/Resource/Examples/PageSetup/SheetTab.xlsx
@@ -363,16 +363,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="1" gridLines="1"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="overThenDown" orientation="default" blackAndWhite="1" draft="1" cellComments="atEnd" errors="NA"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:printOptions headings="1" gridLines="1"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:pageSetup pageOrder="overThenDown" blackAndWhite="1" draft="1" cellComments="atEnd" errors="NA"/>
 </x:worksheet>
 </file>